--- a/docs/Atrium要件定義書 ・ユースケース図.xlsx
+++ b/docs/Atrium要件定義書 ・ユースケース図.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagayamarina/Desktop/Atrium/Atrium/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84455976-D76B-7548-94E3-77BACF840210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="機能要件" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="画面要件" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="ユースケース図" sheetId="3" r:id="rId7"/>
+    <sheet name="機能要件" sheetId="1" r:id="rId1"/>
+    <sheet name="画面要件" sheetId="2" r:id="rId2"/>
+    <sheet name="ユースケース図" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -82,19 +91,26 @@
   </si>
   <si>
     <r>
-      <rPr/>
       <t>Canvas API (MDN)
 (</t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://developer.mozilla.org/ja/docs/Web/API/Canvas_API</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>)</t>
     </r>
   </si>
@@ -142,63 +158,10 @@
     <t>クレカ決済</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1F1F1F"/>
-      </rPr>
-      <t>Stripe　（</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://stripe.com/docs/api</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1F1F1F"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>いいね・レビュー投稿</t>
   </si>
   <si>
-    <t>購入履歴のある商品に1回のみ投稿可能
-AIが不適切な内容を自動で弾く</t>
-  </si>
-  <si>
     <t>商品評価、 コメント</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1F1F1F"/>
-      </rPr>
-      <t>OpenAI Moderation
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://platform.openai.com/docs/guides/moderation</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="&quot;Google Sans Text&quot;, sans-serif !important"/>
-        <color rgb="FF1F1F1F"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>通知</t>
@@ -241,9 +204,6 @@
     <t>不適切な商品の削除</t>
   </si>
   <si>
-    <t>不適切商品消去、AI検閲ログ確認</t>
-  </si>
-  <si>
     <t>管理者</t>
   </si>
   <si>
@@ -379,49 +339,351 @@
   </si>
   <si>
     <t>リンク遷移でログアウトしトップ画面に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入履歴のある商品に1回のみ投稿可能
+AIが不適切な内容を自動で弾く </t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stripe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>　（</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://stripe.com/docs/api</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OpenAI Moderation(</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://platform.openai.com/docs/guides/moderation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>による自動検閲は今回の実装対象外。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NG</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ワード置換処理のみ実装。</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>不適切商品消去、AI検閲ログ確認</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>※AI検閲ログ確認は今回の実装対象外。管理者による商品削除・非公開化は実装済み。</t>
+  </si>
+  <si>
+    <r>
+      <t>OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Tsukushi A Round Gothic Bold"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>による</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="&quot;Google Sans Text&quot;"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Tsukushi A Round Gothic Bold"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>判定は未実装</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="&quot;Google Sans Text&quot;"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>検閲ログ確認は未実装</t>
+    </r>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m-d"/>
+    <numFmt numFmtId="176" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="7">
-    <font>
-      <sz val="10.0"/>
+  <fonts count="19">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
-      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Tsukushi A Round Gothic Bold"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,64 +691,65 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -497,11 +760,17 @@
     <xdr:ext cx="11934825" cy="5172075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="画像"/>
+        <xdr:cNvPr id="2" name="image1.png" title="画像">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -523,7 +792,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -713,26 +982,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC9DAF8"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B3:G19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.13"/>
-    <col customWidth="1" min="3" max="3" width="26.75"/>
-    <col customWidth="1" min="4" max="4" width="50.5"/>
-    <col customWidth="1" min="5" max="5" width="45.25"/>
-    <col customWidth="1" min="6" max="6" width="17.63"/>
-    <col customWidth="1" min="7" max="7" width="28.0"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="50.5" customWidth="1"/>
+    <col min="5" max="5" width="45.1640625" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="2:7" ht="15.75" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -752,9 +1024,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:7" ht="15.75" customHeight="1">
       <c r="B4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -770,9 +1042,9 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="2:7" ht="15.75" customHeight="1">
       <c r="B5" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -786,9 +1058,9 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="2:7" ht="15.75" customHeight="1">
       <c r="B6" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -804,9 +1076,9 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="2:7" ht="15.75" customHeight="1">
       <c r="B7" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -822,9 +1094,9 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="2:7" ht="15.75" customHeight="1">
       <c r="B8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -842,9 +1114,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:7" ht="15.75" customHeight="1">
       <c r="B9" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>23</v>
@@ -860,9 +1132,9 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="2:7" ht="15.75" customHeight="1">
       <c r="B10" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>26</v>
@@ -878,9 +1150,9 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="2:7" ht="15.75" customHeight="1">
       <c r="B11" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -896,9 +1168,9 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="2:7" ht="15.75" customHeight="1">
       <c r="B12" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -913,9 +1185,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:7" ht="15.75" customHeight="1">
       <c r="B13" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
@@ -927,405 +1199,420 @@
       <c r="F13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="15.75" customHeight="1">
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="15.75" customHeight="1">
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="2:7" ht="15.75" customHeight="1">
       <c r="B16" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:7" ht="15.75" customHeight="1">
       <c r="B17" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="2:7" ht="15.75" customHeight="1">
       <c r="B18" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:7" ht="15.75" customHeight="1">
       <c r="B19" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G8"/>
-    <hyperlink r:id="rId2" ref="G13"/>
-    <hyperlink r:id="rId3" ref="G14"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G14" r:id="rId3" display="OpenAI Moderation_x000a_(https://platform.openai.com/docs/guides/moderation)" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFB4A7D6"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B3:F19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="32.75"/>
-    <col customWidth="1" min="4" max="4" width="51.88"/>
-    <col customWidth="1" min="5" max="5" width="43.38"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="51.83203125" customWidth="1"/>
+    <col min="5" max="5" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="2:6" ht="15.75" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5">
-      <c r="B5" s="7">
-        <v>2.0</v>
+    <row r="5" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B5" s="6">
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B6" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="8">
-        <v>46055.0</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B8" s="6">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B10" s="7">
+        <v>46144</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B11" s="7">
+        <v>46145</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="8">
-        <v>46144.0</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B12" s="6">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="8">
-        <v>46145.0</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B13" s="7">
+        <v>46175</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B14" s="6">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="8">
-        <v>46175.0</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B15" s="6">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F15" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B16" s="6">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F16" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B17" s="6">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B18" s="6">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B19" s="4">
+        <v>12</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="7">
-        <v>11.0</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFEAD1DC"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData/>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>